--- a/BWI/bestwine_output/bestwine_Cambodia.xlsx
+++ b/BWI/bestwine_output/bestwine_Cambodia.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2248,111 @@
       <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Vinissimo Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vinissimo Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>53843</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Cambodia</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Phnom Penh</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Phnom Penh</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>70a Street 1990</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinissimo.asia</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>sarapich.pin@vinissimo.asia</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>00022145</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinissimoasia/</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/vinissimoasia</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Vinissimo</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Sarapich Pin</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarapichpin</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
